--- a/nutrition_app/data/mdhs_datasets.xlsx
+++ b/nutrition_app/data/mdhs_datasets.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\__CODE\R\nutrition\nutrition_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DA8BF7-53F9-4642-9B99-B4EE2C709CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED7DE4F-826E-4A4D-9BAB-0D6516989AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="782" activeTab="3" xr2:uid="{7A3AA210-3982-447C-A034-1318D06313F9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="782" activeTab="4" xr2:uid="{7A3AA210-3982-447C-A034-1318D06313F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Stunting " sheetId="3" r:id="rId1"/>
     <sheet name="Wasting" sheetId="4" r:id="rId2"/>
     <sheet name="underweight" sheetId="5" r:id="rId3"/>
     <sheet name="nutrition_trend" sheetId="2" r:id="rId4"/>
+    <sheet name="aggregates" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="75">
   <si>
     <t>Chitipa</t>
   </si>
@@ -255,6 +256,15 @@
   </si>
   <si>
     <t>District</t>
+  </si>
+  <si>
+    <t>Percentage_below_ -2SD_stunting</t>
+  </si>
+  <si>
+    <t>Percentage_below_-2SD_wasting</t>
+  </si>
+  <si>
+    <t>percentage below_-2SD_underweight</t>
   </si>
 </sst>
 </file>
@@ -2566,4 +2576,482 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C784AFC6-3684-4861-828C-71D40BBA0F69}">
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>50.8</v>
+      </c>
+      <c r="C2">
+        <v>2.5</v>
+      </c>
+      <c r="D2">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>25.8</v>
+      </c>
+      <c r="C3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>22.5</v>
+      </c>
+      <c r="C4">
+        <v>1.4</v>
+      </c>
+      <c r="D4">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>31.7</v>
+      </c>
+      <c r="C5">
+        <v>2.5</v>
+      </c>
+      <c r="D5">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>36.9</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="D6">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>23.8</v>
+      </c>
+      <c r="C7">
+        <v>17.3</v>
+      </c>
+      <c r="D7">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>24.7</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>38.1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D9">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>32.5</v>
+      </c>
+      <c r="C10">
+        <v>5.3</v>
+      </c>
+      <c r="D10">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>30.2</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>44.7</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="C13">
+        <v>4.2</v>
+      </c>
+      <c r="D13">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>35.6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="D14">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>41.5</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>36.6</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19">
+        <v>40.6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D19">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>43.6</v>
+      </c>
+      <c r="C20">
+        <v>0.8</v>
+      </c>
+      <c r="D20">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>41.7</v>
+      </c>
+      <c r="C21">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D21">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22">
+        <v>38.4</v>
+      </c>
+      <c r="C22">
+        <v>1.8</v>
+      </c>
+      <c r="D22">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>30.6</v>
+      </c>
+      <c r="C23">
+        <v>0.9</v>
+      </c>
+      <c r="D23">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>42.6</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25">
+        <v>33.9</v>
+      </c>
+      <c r="C25">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D25">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26">
+        <v>33.6</v>
+      </c>
+      <c r="C26">
+        <v>1.5</v>
+      </c>
+      <c r="D26">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27">
+        <v>38.9</v>
+      </c>
+      <c r="C27">
+        <v>2.7</v>
+      </c>
+      <c r="D27">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="C28">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D28">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C29">
+        <v>2.8</v>
+      </c>
+      <c r="D29">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="C30">
+        <v>3.3</v>
+      </c>
+      <c r="D30">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <v>50</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>31.1</v>
+      </c>
+      <c r="C32">
+        <v>1.3</v>
+      </c>
+      <c r="D32">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33">
+        <v>41.5</v>
+      </c>
+      <c r="C33">
+        <v>1.3</v>
+      </c>
+      <c r="D33">
+        <v>4.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>